--- a/work_request_forms/042_tooling_design_update_request_form--work_request_forms.xlsx
+++ b/work_request_forms/042_tooling_design_update_request_form--work_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'tooling',_'label':_'tooling'}</t>
+          <t>tooling</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Tooling', 'label': 'Tooling'}</t>
+          <t>Tooling</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'machining',_'label':_'machining'}</t>
+          <t>machining</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Machining', 'label': 'Machining'}</t>
+          <t>Machining</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'welding',_'label':_'welding'}</t>
+          <t>welding</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Welding', 'label': 'Welding'}</t>
+          <t>Welding</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'major',_'label':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Major', 'label': 'Major'}</t>
+          <t>Major</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'minor',_'label':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Minor', 'label': 'Minor'}</t>
+          <t>Minor</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'major/minor',_'label':_'major/minor'}</t>
+          <t>major/minor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Major/Minor', 'label': 'Major/Minor'}</t>
+          <t>Major/Minor</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'rejected',_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected', 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'submit',_'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'submit', 'label': 'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'save_for_later',_'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'save_for_later', 'label': 'save_for_later'}</t>
+          <t>save for later</t>
         </is>
       </c>
     </row>
